--- a/artfynd/A 50212-2025 artfynd.xlsx
+++ b/artfynd/A 50212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118242827</v>
+        <v>119286245</v>
       </c>
       <c r="B2" t="n">
-        <v>97752</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>525426</v>
+        <v>525423</v>
       </c>
       <c r="R2" t="n">
-        <v>7049691</v>
+        <v>7049678</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118242828</v>
+        <v>119286246</v>
       </c>
       <c r="B3" t="n">
-        <v>97752</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>525239</v>
+        <v>525427</v>
       </c>
       <c r="R3" t="n">
-        <v>7049554</v>
+        <v>7049685</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118242822</v>
+        <v>119286247</v>
       </c>
       <c r="B4" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>525399</v>
+        <v>525426</v>
       </c>
       <c r="R4" t="n">
-        <v>7049660</v>
+        <v>7049691</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118242821</v>
+        <v>119286248</v>
       </c>
       <c r="B5" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>504</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>525399</v>
+        <v>525239</v>
       </c>
       <c r="R5" t="n">
-        <v>7049660</v>
+        <v>7049554</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118242825</v>
+        <v>119286243</v>
       </c>
       <c r="B6" t="n">
-        <v>97752</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>504</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>525423</v>
+        <v>525363</v>
       </c>
       <c r="R6" t="n">
-        <v>7049678</v>
+        <v>7049675</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,12 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118242819</v>
+        <v>119286239</v>
       </c>
       <c r="B7" t="n">
-        <v>90500</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1255,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,15 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118242820</v>
+        <v>119286240</v>
       </c>
       <c r="B8" t="n">
-        <v>79565</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,15 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118242824</v>
+        <v>119286242</v>
       </c>
       <c r="B9" t="n">
-        <v>90522</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1405,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>525275</v>
+        <v>525399</v>
       </c>
       <c r="R9" t="n">
-        <v>7049556</v>
+        <v>7049660</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1459,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1491,15 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118242826</v>
+        <v>119286241</v>
       </c>
       <c r="B10" t="n">
-        <v>97752</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>504</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>525427</v>
+        <v>525399</v>
       </c>
       <c r="R10" t="n">
-        <v>7049685</v>
+        <v>7049660</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-01-02</t>
+          <t>2024-07-02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1590,108 +1545,6 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>118242823</v>
-      </c>
-      <c r="B11" t="n">
-        <v>90788</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>658</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Rhodofomes roseus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Grossmyrberget, Jmt</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>525363</v>
-      </c>
-      <c r="R11" t="n">
-        <v>7049675</v>
-      </c>
-      <c r="S11" t="n">
-        <v>10</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Hammerdal</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2024-01-02</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2024-01-02</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Noel Wieser</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50212-2025 artfynd.xlsx
+++ b/artfynd/A 50212-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286245</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286246</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286247</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286248</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286243</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286239</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286240</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286242</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,8 +1590,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119286241</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>